--- a/ZeroDollarError.xlsx
+++ b/ZeroDollarError.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91560CD8-23EA-4CFD-AE5A-2700B6BF56FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F726127-4767-457B-9DC3-F9C146543995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8205" yWindow="3120" windowWidth="17400" windowHeight="11655" xr2:uid="{BE3AB41B-52E7-4F75-B611-BEDC20D061FE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{BE3AB41B-52E7-4F75-B611-BEDC20D061FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="56">
   <si>
     <t>TestNotes</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>12/29</t>
   </si>
 </sst>
 </file>
@@ -270,9 +273,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -310,7 +313,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -416,7 +419,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -558,7 +561,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -567,28 +570,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E18F0A-E29B-4622-B46D-88CFDF71BC3A}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.265625" style="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
@@ -682,7 +685,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -723,7 +726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -764,7 +767,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
@@ -805,7 +808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -846,7 +849,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
@@ -887,7 +890,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -934,7 +937,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -981,7 +984,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>24</v>
@@ -1066,7 +1069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>24</v>
@@ -1104,7 +1107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>22</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>24</v>
@@ -1142,7 +1145,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1171,7 +1174,7 @@
         <v>22</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>24</v>
@@ -1189,28 +1192,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4E1D0F-C785-47D4-BAEF-9A0B9A488798}">
   <dimension ref="A1:Q5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.265625" style="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -1301,7 +1304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -1377,7 +1380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
